--- a/Team-Data/2013-14/4-4-2013-14.xlsx
+++ b/Team-Data/2013-14/4-4-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.44</v>
+        <v>0.432</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J2" t="n">
         <v>81.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
         <v>25.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O2" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0.78</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S2" t="n">
         <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
@@ -733,25 +800,25 @@
         <v>19.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -763,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -772,10 +839,10 @@
         <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -793,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>26</v>
@@ -805,16 +872,16 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>0.303</v>
+        <v>0.307</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
         <v>83.8</v>
@@ -870,10 +937,10 @@
         <v>6.7</v>
       </c>
       <c r="M3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
         <v>16.3</v>
@@ -885,7 +952,7 @@
         <v>0.775</v>
       </c>
       <c r="R3" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
         <v>30.7</v>
@@ -894,13 +961,13 @@
         <v>42.7</v>
       </c>
       <c r="U3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X3" t="n">
         <v>4.3</v>
@@ -909,34 +976,34 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>19.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ3" t="n">
         <v>10</v>
@@ -954,25 +1021,25 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.547</v>
+        <v>0.541</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
       </c>
       <c r="M4" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O4" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.759</v>
       </c>
       <c r="R4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>8.6</v>
@@ -1094,13 +1161,13 @@
         <v>21.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
         <v>25</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
@@ -1148,34 +1215,34 @@
         <v>29</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1246,7 +1313,7 @@
         <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R5" t="n">
         <v>9.4</v>
@@ -1264,28 +1331,28 @@
         <v>12.3</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
         <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1303,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
         <v>24</v>
@@ -1312,13 +1379,13 @@
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1333,10 +1400,10 @@
         <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,16 +1415,16 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.579</v>
+        <v>0.573</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
         <v>80.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L6" t="n">
         <v>6.1</v>
@@ -1422,19 +1489,19 @@
         <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S6" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T6" t="n">
         <v>44.4</v>
@@ -1443,7 +1510,7 @@
         <v>22.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1452,22 +1519,22 @@
         <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="n">
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1488,22 +1555,22 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
         <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN6" t="n">
         <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1521,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1533,7 +1600,7 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
@@ -1589,46 +1656,46 @@
         <v>36.7</v>
       </c>
       <c r="J7" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
         <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U7" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X7" t="n">
         <v>3.7</v>
@@ -1646,10 +1713,10 @@
         <v>97.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1670,7 +1737,7 @@
         <v>9</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1682,16 +1749,16 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
         <v>15</v>
@@ -1718,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
@@ -1771,10 +1838,10 @@
         <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
         <v>8.800000000000001</v>
@@ -1783,28 +1850,28 @@
         <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>13.6</v>
@@ -1819,7 +1886,7 @@
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" t="n">
         <v>20.1</v>
@@ -1828,10 +1895,10 @@
         <v>105.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,13 +1910,13 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1873,10 +1940,10 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>26</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" t="n">
         <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>0.434</v>
+        <v>0.44</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J9" t="n">
         <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L9" t="n">
         <v>8.5</v>
@@ -1965,16 +2032,16 @@
         <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R9" t="n">
         <v>12.1</v>
@@ -1986,10 +2053,10 @@
         <v>45.1</v>
       </c>
       <c r="U9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
@@ -2001,28 +2068,28 @@
         <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.9</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2073,13 +2140,13 @@
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
         <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2144,7 +2211,7 @@
         <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N10" t="n">
         <v>0.319</v>
@@ -2153,16 +2220,16 @@
         <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.668</v>
+        <v>0.669</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
         <v>45.2</v>
@@ -2192,10 +2259,10 @@
         <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2219,7 +2286,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2243,10 +2310,10 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2261,13 +2328,13 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB10" t="n">
         <v>17</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
         <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.618</v>
+        <v>0.613</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J11" t="n">
-        <v>84.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.459</v>
@@ -2326,31 +2393,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T11" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2368,16 +2435,16 @@
         <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB11" t="n">
         <v>103.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2401,7 +2468,7 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2422,10 +2489,10 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
@@ -2434,7 +2501,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2446,13 +2513,13 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2508,25 +2575,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P12" t="n">
         <v>31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.707</v>
+        <v>0.704</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T12" t="n">
         <v>45.1</v>
@@ -2535,7 +2602,7 @@
         <v>21.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
@@ -2544,7 +2611,7 @@
         <v>5.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
         <v>20.4</v>
@@ -2610,7 +2677,7 @@
         <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,7 +2686,7 @@
         <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -2663,40 +2730,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J13" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
         <v>23.4</v>
@@ -2708,16 +2775,16 @@
         <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="T13" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U13" t="n">
         <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
@@ -2738,22 +2805,22 @@
         <v>96.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
       </c>
       <c r="AF13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG13" t="n">
         <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2771,10 +2838,10 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -2792,28 +2859,28 @@
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -2929,31 +2996,31 @@
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2980,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -2992,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J15" t="n">
         <v>85</v>
@@ -3057,13 +3124,13 @@
         <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O15" t="n">
         <v>16.9</v>
       </c>
       <c r="P15" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q15" t="n">
         <v>0.755</v>
@@ -3075,7 +3142,7 @@
         <v>32</v>
       </c>
       <c r="T15" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U15" t="n">
         <v>24.1</v>
@@ -3084,7 +3151,7 @@
         <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X15" t="n">
         <v>5.6</v>
@@ -3093,19 +3160,19 @@
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3138,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3165,13 +3232,13 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>0.592</v>
+        <v>0.587</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J16" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="P16" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="R16" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3275,19 +3342,19 @@
         <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3299,13 +3366,13 @@
         <v>10</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
         <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,19 +3384,19 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ16" t="n">
         <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
@@ -3350,7 +3417,7 @@
         <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
         <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="H17" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.503</v>
+        <v>0.504</v>
       </c>
       <c r="L17" t="n">
         <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="U17" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V17" t="n">
         <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X17" t="n">
         <v>4.6</v>
@@ -3457,16 +3524,16 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>103</v>
+        <v>102.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -3478,13 +3545,13 @@
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3505,7 +3572,7 @@
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,13 +3590,13 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>0.184</v>
+        <v>0.187</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.352</v>
       </c>
       <c r="O18" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.751</v>
@@ -3621,19 +3688,19 @@
         <v>29.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
@@ -3645,13 +3712,13 @@
         <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,16 +3730,16 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
         <v>20</v>
@@ -3681,28 +3748,28 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
       </c>
       <c r="AP18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>20</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
         <v>24</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>18</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
         <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.444</v>
@@ -3782,31 +3849,31 @@
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
         <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R19" t="n">
         <v>12.5</v>
       </c>
       <c r="S19" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
         <v>44.9</v>
       </c>
       <c r="U19" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
@@ -3821,13 +3888,13 @@
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA19" t="n">
         <v>23.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.9</v>
+        <v>106.6</v>
       </c>
       <c r="AC19" t="n">
         <v>3.2</v>
@@ -3845,16 +3912,16 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
@@ -3902,10 +3969,10 @@
         <v>3</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>0.421</v>
+        <v>0.427</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
@@ -3955,7 +4022,7 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.46</v>
@@ -3976,7 +4043,7 @@
         <v>23.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
@@ -3985,7 +4052,7 @@
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
@@ -4003,7 +4070,7 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA20" t="n">
         <v>20.4</v>
@@ -4015,10 +4082,10 @@
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
@@ -4027,13 +4094,13 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4045,10 +4112,10 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP20" t="n">
         <v>12</v>
@@ -4057,7 +4124,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4081,7 +4148,7 @@
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA20" t="n">
         <v>18</v>
@@ -4090,7 +4157,7 @@
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
         <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.429</v>
+        <v>0.434</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4146,19 +4213,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O21" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P21" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R21" t="n">
         <v>10.7</v>
@@ -4167,7 +4234,7 @@
         <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
         <v>20.3</v>
@@ -4185,19 +4252,19 @@
         <v>3.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>-1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4206,34 +4273,34 @@
         <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>14</v>
       </c>
       <c r="AL21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM21" t="n">
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
@@ -4269,10 +4336,10 @@
         <v>24</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
         <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.733</v>
+        <v>0.743</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,28 +4386,28 @@
         <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O22" t="n">
         <v>19.9</v>
       </c>
       <c r="P22" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="R22" t="n">
         <v>10.8</v>
@@ -4358,7 +4425,7 @@
         <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
@@ -4367,16 +4434,16 @@
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="AD22" t="n">
         <v>25</v>
@@ -4397,13 +4464,13 @@
         <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4415,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4424,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>0.276</v>
+        <v>0.28</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4504,16 +4571,16 @@
         <v>83.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O23" t="n">
         <v>16.1</v>
@@ -4522,7 +4589,7 @@
         <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
         <v>9.699999999999999</v>
@@ -4534,7 +4601,7 @@
         <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
@@ -4543,25 +4610,25 @@
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4585,19 +4652,19 @@
         <v>23</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>21</v>
       </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4615,25 +4682,25 @@
         <v>22</v>
       </c>
       <c r="AV23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW23" t="n">
         <v>15</v>
       </c>
-      <c r="AW23" t="n">
-        <v>14</v>
-      </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>0.224</v>
+        <v>0.213</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4683,13 +4750,13 @@
         <v>37.7</v>
       </c>
       <c r="J24" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M24" t="n">
         <v>22.7</v>
@@ -4698,22 +4765,22 @@
         <v>0.31</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R24" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T24" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U24" t="n">
         <v>21.9</v>
@@ -4734,16 +4801,16 @@
         <v>22.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.9</v>
+        <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,16 +4822,16 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL24" t="n">
         <v>19</v>
@@ -4791,7 +4858,7 @@
         <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.592</v>
+        <v>0.587</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,43 +4932,43 @@
         <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L25" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P25" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U25" t="n">
         <v>19.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
         <v>8.300000000000001</v>
@@ -4910,22 +4977,22 @@
         <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4940,40 +5007,40 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>29</v>
@@ -4982,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>24</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E26" t="n">
         <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.636</v>
+        <v>0.645</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J26" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M26" t="n">
         <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P26" t="n">
         <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
         <v>12.5</v>
@@ -5080,10 +5147,10 @@
         <v>46.3</v>
       </c>
       <c r="U26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W26" t="n">
         <v>5.5</v>
@@ -5095,22 +5162,22 @@
         <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA26" t="n">
         <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.7</v>
+        <v>106.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5122,16 +5189,16 @@
         <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5179,10 +5246,10 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
         <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O27" t="n">
         <v>20.8</v>
       </c>
       <c r="P27" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R27" t="n">
         <v>12.2</v>
@@ -5259,10 +5326,10 @@
         <v>32.3</v>
       </c>
       <c r="T27" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V27" t="n">
         <v>15.4</v>
@@ -5277,19 +5344,19 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA27" t="n">
         <v>23.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.7</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5307,13 +5374,13 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM27" t="n">
         <v>26</v>
@@ -5334,7 +5401,7 @@
         <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5361,10 +5428,10 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5507,7 +5574,7 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.579</v>
+        <v>0.573</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.444</v>
@@ -5605,13 +5672,13 @@
         <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0.782</v>
@@ -5626,7 +5693,7 @@
         <v>42.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
         <v>14.2</v>
@@ -5641,7 +5708,7 @@
         <v>4.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
@@ -5650,10 +5717,10 @@
         <v>100.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5674,10 +5741,10 @@
         <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM29" t="n">
         <v>11</v>
@@ -5713,19 +5780,19 @@
         <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5757,85 +5824,85 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
         <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>0.316</v>
+        <v>0.307</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N30" t="n">
         <v>0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P30" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S30" t="n">
         <v>30.2</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.8</v>
+        <v>-7</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5865,13 +5932,13 @@
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
@@ -5886,19 +5953,19 @@
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV30" t="n">
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
         <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0.526</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
@@ -5957,7 +6024,7 @@
         <v>38.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.457</v>
@@ -5969,16 +6036,16 @@
         <v>20.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
         <v>10.9</v>
@@ -5990,34 +6057,34 @@
         <v>42.3</v>
       </c>
       <c r="U31" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
         <v>14.8</v>
       </c>
       <c r="W31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC31" t="n">
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,16 +6099,16 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6065,7 +6132,7 @@
         <v>17</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6077,10 +6144,10 @@
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
@@ -6089,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-4-2013-14</t>
+          <t>2014-04-04</t>
         </is>
       </c>
     </row>
